--- a/Config/Datas/body_part.xlsx
+++ b/Config/Datas/body_part.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="body_part_def" sheetId="1" r:id="rId1"/>
     <sheet name="body_part_level" sheetId="2" r:id="rId2"/>
-    <sheet name="body_part_talent_info" sheetId="4" r:id="rId3"/>
+    <sheet name="body_part_progress_info" sheetId="4" r:id="rId3"/>
     <sheet name="part_local_attr_def" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -125,6 +125,15 @@
     <t>global_bonuses</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>h_power</t>
+  </si>
+  <si>
+    <t>absorb_rate</t>
+  </si>
+  <si>
     <t>local_bonuses</t>
   </si>
   <si>
@@ -140,61 +149,55 @@
     <t>1,100</t>
   </si>
   <si>
+    <t>1,150</t>
+  </si>
+  <si>
+    <t>2,50</t>
+  </si>
+  <si>
+    <t>1,80</t>
+  </si>
+  <si>
+    <t>1,120</t>
+  </si>
+  <si>
+    <t>3,20</t>
+  </si>
+  <si>
+    <t>1,60</t>
+  </si>
+  <si>
+    <t>2,40</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>passive_skill_id</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>全局被动效果</t>
+  </si>
+  <si>
+    <t>口部5级效果</t>
+  </si>
+  <si>
     <t>10,1</t>
   </si>
   <si>
-    <t>1,150</t>
-  </si>
-  <si>
-    <t>10,1|2,500</t>
-  </si>
-  <si>
-    <t>2,50</t>
-  </si>
-  <si>
-    <t>1,80</t>
-  </si>
-  <si>
     <t>11,1</t>
   </si>
   <si>
-    <t>1,120</t>
-  </si>
-  <si>
-    <t>11,1|2,300</t>
-  </si>
-  <si>
-    <t>3,20</t>
-  </si>
-  <si>
-    <t>1,60</t>
-  </si>
-  <si>
     <t>12,1</t>
   </si>
   <si>
-    <t>2,40</t>
-  </si>
-  <si>
-    <t>15,0</t>
-  </si>
-  <si>
-    <t>15,1</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>passive_skill_id</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全局被动效果</t>
-  </si>
-  <si>
-    <t>口部5级效果</t>
+    <t>13,1</t>
   </si>
   <si>
     <t>attr_id</t>
@@ -207,15 +210,6 @@
   </si>
   <si>
     <t>耐受</t>
-  </si>
-  <si>
-    <t>体液增益</t>
-  </si>
-  <si>
-    <t>自控抵抗</t>
-  </si>
-  <si>
-    <t>外泄</t>
   </si>
 </sst>
 </file>
@@ -228,14 +222,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,148 +678,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1186,6 +1173,10 @@
   <sheetPr/>
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <cols>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="20.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
@@ -1412,14 +1403,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="5" max="5" width="25.25" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="24.5" customWidth="1"/>
+    <col min="7" max="8" width="25.25" customWidth="1"/>
+    <col min="9" max="9" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1438,8 +1431,17 @@
       <c r="F1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1450,16 +1452,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1478,8 +1489,17 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="B4" t="s">
         <v>15</v>
       </c>
@@ -1492,11 +1512,20 @@
       <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4">
+        <v>50000</v>
+      </c>
+      <c r="G4">
+        <v>50000</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -1506,14 +1535,20 @@
       <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5">
+        <v>60000</v>
+      </c>
+      <c r="G5">
+        <v>60000</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -1523,14 +1558,20 @@
       <c r="D6">
         <v>300</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F6">
+        <v>70000</v>
+      </c>
+      <c r="G6">
+        <v>70000</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8" t="s">
         <v>18</v>
       </c>
@@ -1540,14 +1581,20 @@
       <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8">
+        <v>50000</v>
+      </c>
+      <c r="G8">
+        <v>50000</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -1557,14 +1604,20 @@
       <c r="D9">
         <v>100</v>
       </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="F9">
+        <v>50000</v>
+      </c>
+      <c r="G9">
+        <v>50000</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:9">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -1574,78 +1627,108 @@
       <c r="D10">
         <v>300</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10">
+        <v>50000</v>
+      </c>
+      <c r="G10">
+        <v>50000</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10" t="s">
         <v>43</v>
       </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:9">
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>50000</v>
+      </c>
+      <c r="G12">
+        <v>50000</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
         <v>2</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>120</v>
       </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" t="s">
+      <c r="F13">
+        <v>50000</v>
+      </c>
+      <c r="G13">
+        <v>50000</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>1</v>
       </c>
-      <c r="D13">
+      <c r="D15">
         <v>0</v>
       </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="F15">
+        <v>50000</v>
+      </c>
+      <c r="G15">
+        <v>50000</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+      <c r="I15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="B14" t="s">
+    <row r="16" spans="1:9">
+      <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C14">
+      <c r="C16">
         <v>2</v>
       </c>
-      <c r="D14">
+      <c r="D16">
         <v>50</v>
       </c>
-      <c r="E14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="F16">
+        <v>50000</v>
+      </c>
+      <c r="G16">
+        <v>50000</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1658,51 +1741,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="12.375" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="25.25" customWidth="1"/>
-    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="3" max="3" width="12.375" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="11.625" customWidth="1"/>
+    <col min="6" max="6" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="25.25" customWidth="1"/>
+    <col min="8" max="8" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" t="s">
-        <v>50</v>
-      </c>
       <c r="E1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1718,126 +1814,177 @@
       <c r="E3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
         <v>52</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
+    <row r="11" spans="1:7">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
         <v>54</v>
       </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1849,21 +1996,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1899,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4">
         <v>10000</v>
@@ -1910,42 +2057,9 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8">
         <v>10000</v>
       </c>
     </row>

--- a/Config/Datas/body_part.xlsx
+++ b/Config/Datas/body_part.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="body_part_def" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -92,28 +92,22 @@
     <t>胸</t>
   </si>
   <si>
-    <t>Womb</t>
-  </si>
-  <si>
-    <t>腹</t>
-  </si>
-  <si>
-    <t>Tail</t>
-  </si>
-  <si>
-    <t>尾</t>
-  </si>
-  <si>
-    <t>Wing</t>
-  </si>
-  <si>
-    <t>翼</t>
-  </si>
-  <si>
-    <t>Skin</t>
-  </si>
-  <si>
-    <t>肤</t>
+    <t>Pussy</t>
+  </si>
+  <si>
+    <t>穴</t>
+  </si>
+  <si>
+    <t>Hip</t>
+  </si>
+  <si>
+    <t>尻</t>
+  </si>
+  <si>
+    <t>Limb</t>
+  </si>
+  <si>
+    <t>肢体</t>
   </si>
   <si>
     <t>level</t>
@@ -191,13 +185,25 @@
     <t>10,1</t>
   </si>
   <si>
+    <t>乳 5级效果</t>
+  </si>
+  <si>
     <t>11,1</t>
   </si>
   <si>
+    <t>穴 5级效果</t>
+  </si>
+  <si>
     <t>12,1</t>
   </si>
   <si>
+    <t>尻 5级效果</t>
+  </si>
+  <si>
     <t>13,1</t>
+  </si>
+  <si>
+    <t>肢体 5级效果</t>
   </si>
   <si>
     <t>attr_id</t>
@@ -1171,9 +1177,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="20.125" customWidth="1"/>
   </cols>
@@ -1368,29 +1375,6 @@
         <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-      <c r="H9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1403,7 +1387,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="5" max="5" width="18.5" customWidth="1"/>
@@ -1420,25 +1404,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>32</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1452,22 +1436,22 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
         <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1522,7 +1506,7 @@
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1545,7 +1529,7 @@
         <v>5</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1568,7 +1552,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1591,7 +1575,7 @@
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1614,7 +1598,7 @@
         <v>5</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1637,7 +1621,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1660,7 +1644,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1683,12 +1667,12 @@
         <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1706,12 +1690,12 @@
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="B16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -1729,7 +1713,53 @@
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>50000</v>
+      </c>
+      <c r="G18">
+        <v>50000</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>50000</v>
+      </c>
+      <c r="G19">
+        <v>50000</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1741,7 +1771,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="12.375" customWidth="1"/>
@@ -1757,22 +1787,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" t="s">
-        <v>30</v>
-      </c>
       <c r="G1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1792,7 +1822,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -1823,18 +1853,18 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -1843,7 +1873,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -1851,7 +1881,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -1860,12 +1890,12 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1874,35 +1904,21 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E9" t="s">
         <v>51</v>
@@ -1910,81 +1926,126 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10">
-        <v>6</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
         <v>51</v>
       </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
+      <c r="F11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13">
-        <v>9</v>
+        <v>300</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="B14">
-        <v>10</v>
+        <v>301</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16">
+        <v>400</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17">
+        <v>401</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19">
+        <v>500</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20">
+        <v>501</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2004,13 +2065,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2046,7 +2107,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4">
         <v>10000</v>
@@ -2057,7 +2118,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5">
         <v>10000</v>

--- a/Config/Datas/body_part.xlsx
+++ b/Config/Datas/body_part.xlsx
@@ -1185,11 +1185,9 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1208,11 +1206,9 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -1231,11 +1227,9 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -1254,11 +1248,9 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1277,11 +1269,9 @@
       <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -1300,11 +1290,9 @@
       <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>6</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1479,7 +1467,6 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>50000</v>
       </c>
@@ -1935,7 +1922,6 @@
           <t>##</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>全局被动效果</t>
@@ -1959,7 +1945,6 @@
           <t>口部5级效果</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1998,7 +1983,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>10,None,1</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2043,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11,1</t>
+          <t>11,None,1</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2085,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>12,1</t>
+          <t>12,None,1</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2127,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>13,None,1</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2169,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>13,None,1</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/body_part.xlsx
+++ b/Config/Datas/body_part.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="body_part_def" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="body_part_level" sheetId="2" state="visible" r:id="rId2"/>
@@ -12,7 +9,6 @@
     <sheet name="part_local_attr_def" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -22,154 +18,112 @@
   <fonts count="20">
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color theme="0"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -182,198 +136,161 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
@@ -387,25 +304,16 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -420,7 +328,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -435,7 +342,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -450,44 +356,36 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -496,7 +394,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -624,57 +522,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -789,72 +686,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -910,7 +749,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -919,13 +758,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -959,17 +798,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1024,7 +852,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
@@ -1035,7 +862,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.75" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -1295,7 +1122,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1347,7 +1174,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>h_power</t>
+          <t>h_technique</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1474,11 +1301,11 @@
         <v>50000</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,100|3,30</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1332,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1,150</t>
+          <t>1,150|3,50</t>
         </is>
       </c>
     </row>
@@ -1528,15 +1355,41 @@
         <v>70000</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2,50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>2,50|3,70</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Breast</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1,80</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
@@ -1544,10 +1397,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
         <v>50000</v>
@@ -1556,11 +1409,11 @@
         <v>50000</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>1,120</t>
         </is>
       </c>
     </row>
@@ -1571,10 +1424,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F9" t="n">
         <v>50000</v>
@@ -1587,21 +1440,21 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1,120</t>
+          <t>3,20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Breast</t>
+          <t>Womb</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>50000</v>
@@ -1610,19 +1463,45 @@
         <v>50000</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3,20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>1,60|3,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Womb</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>120</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2,40|3,120</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Womb</t>
+          <t>Tail</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1638,25 +1517,25 @@
         <v>50000</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1,60</t>
+          <t>1,60|3,50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Womb</t>
+          <t>Tail</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
         <v>50000</v>
@@ -1665,26 +1544,52 @@
         <v>50000</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2,40</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>2,40|3,80</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wing</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1,60</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tail</t>
+          <t>Wing</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
         <v>50000</v>
@@ -1693,98 +1598,20 @@
         <v>50000</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1,60</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tail</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>50</v>
-      </c>
-      <c r="F16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>2,40</t>
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17"/>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Wing</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1,60</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Wing</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>50</v>
-      </c>
-      <c r="F19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2,40</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1987,7 +1814,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" t="n">
         <v>200</v>
@@ -2047,7 +1873,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" t="n">
         <v>300</v>
@@ -2089,7 +1914,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="B16" t="n">
         <v>400</v>
@@ -2131,7 +1955,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" t="n">
         <v>500</v>
@@ -2174,7 +1997,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2184,8 +2007,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2279,7 +2102,46 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>榨取增益</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>控制抗性</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>气场泄漏</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Config/Datas/body_part.xlsx
+++ b/Config/Datas/body_part.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.75" customWidth="1" min="2" max="2"/>
@@ -1040,12 +1040,12 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Womb</t>
+          <t>FrontHole</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>穴</t>
+          <t>前穴</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1061,12 +1061,12 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tail</t>
+          <t>BackHole</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>尻</t>
+          <t>后穴</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1082,7 +1082,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Limb</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1094,31 +1094,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Skin</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>肤</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.5" customWidth="1" min="5" max="5"/>
@@ -1305,7 +1284,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1,100|3,30</t>
+          <t>1,100|3,30|6,1000|7,1000</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1311,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1,150|3,50</t>
+          <t>1,150|3,50|6,200|7,200</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1338,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2,50|3,70</t>
+          <t>2,50|3,70|6,200|7,200</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1365,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>1,80|6,1000|7,1000</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1392,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1,120</t>
+          <t>1,120|6,200|7,200</t>
         </is>
       </c>
     </row>
@@ -1440,14 +1419,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3,20</t>
+          <t>3,20|6,200|7,200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Womb</t>
+          <t>FrontHole</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1467,14 +1446,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1,60|3,80</t>
+          <t>1,60|3,80|6,1000|7,1000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Womb</t>
+          <t>FrontHole</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1494,14 +1473,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2,40|3,120</t>
+          <t>2,40|3,120|6,200|7,200</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tail</t>
+          <t>BackHole</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1521,14 +1500,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1,60|3,50</t>
+          <t>1,60|3,50|6,1000|7,1000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tail</t>
+          <t>BackHole</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1548,14 +1527,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2,40|3,80</t>
+          <t>2,40|3,80|6,200|7,200</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Limb</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1575,14 +1554,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1,60</t>
+          <t>1,60|6,1000|7,1000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Limb</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1602,14 +1581,10 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2,40</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+          <t>2,40|6,200|7,200</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1814,6 +1789,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" t="n">
         <v>200</v>
@@ -1873,13 +1849,14 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" t="n">
         <v>300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Womb</t>
+          <t>FrontHole</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1897,7 +1874,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Womb</t>
+          <t>FrontHole</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1914,13 +1891,14 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" t="n">
         <v>400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tail</t>
+          <t>BackHole</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1938,7 +1916,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tail</t>
+          <t>BackHole</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1955,13 +1933,14 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" t="n">
         <v>500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Limb</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1979,7 +1958,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wing</t>
+          <t>Limb</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2007,7 +1986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -2095,7 +2074,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>耐受</t>
+          <t>高潮阈值</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2108,7 +2087,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>榨取增益</t>
+          <t>榨取力</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -2117,11 +2096,11 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>控制抗性</t>
+          <t>气场泄漏</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2130,15 +2109,28 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>气场泄漏</t>
+          <t>部位H技巧</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10000</v>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>部位H强度</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
